--- a/public/exports-60-250-with-coowners/41333014.xlsx
+++ b/public/exports-60-250-with-coowners/41333014.xlsx
@@ -3514,7 +3514,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311705508</t>
+          <t xml:space="preserve">311705435</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
